--- a/GST/GST 2B Downloader/input.xlsx
+++ b/GST/GST 2B Downloader/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Rohit Python Tools\rohit combo\rohit combo\GST\GST 2B Downloader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADED428-E33E-45D7-A222-C848EF343E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09EC0C0-C017-4EED-B8F9-128047EB0FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>

--- a/GST/GST 2B Downloader/input.xlsx
+++ b/GST/GST 2B Downloader/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Rohit Python Tools\rohit combo\rohit combo\GST\GST 2B Downloader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09EC0C0-C017-4EED-B8F9-128047EB0FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6780EBDA-9BD0-4BC2-B5A9-9415AA094615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>user id</t>
   </si>
@@ -37,12 +37,6 @@
   </si>
   <si>
     <t>Admin@12345</t>
-  </si>
-  <si>
-    <t>gst.rudrakha</t>
-  </si>
-  <si>
-    <t>March@2026</t>
   </si>
 </sst>
 </file>
@@ -385,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" bestFit="1" customWidth="1"/>
@@ -408,18 +402,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{F595CFF3-F1B4-421D-B7A2-2C9CEE3EC477}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{04626507-9F4F-479C-B9D7-BA1BA6000179}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
